--- a/dimarts_16/CAIB_AUXILIAR__Supuesto_181781160818633/CAIB-AUXILIAR, Supuesto-18/datos-supuesto-practico-18.xlsx
+++ b/dimarts_16/CAIB_AUXILIAR__Supuesto_181781160818633/CAIB-AUXILIAR, Supuesto-18/datos-supuesto-practico-18.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/laCie/Trabajos/Cursos interactivos y online/Bárcena/CAIB/2026/CAIB - 2026 - ADMIN/Prácticas/CAIB - ADMIN - supuesto 15/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Documents\oposCaib\dimarts_16\CAIB_AUXILIAR__Supuesto_181781160818633\CAIB-AUXILIAR, Supuesto-18\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8571F0B-2F0F-D44F-813A-163C01009D40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E3FDE6E-7EC7-4440-9249-93E3DA267BDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="64740" yWindow="1740" windowWidth="32540" windowHeight="29960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,21 @@
   <definedNames>
     <definedName name="Excel_BuiltIn__FilterDatabase" localSheetId="0">Hoja1!$A$2:$I$52</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -221,9 +235,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="#,##0&quot; €&quot;"/>
     <numFmt numFmtId="165" formatCode="#,##0.00&quot;    &quot;;#,##0.00&quot;    &quot;;&quot;-&quot;#&quot;    &quot;;&quot; &quot;@&quot; &quot;"/>
+    <numFmt numFmtId="167" formatCode="#,##0\ &quot;€&quot;"/>
   </numFmts>
   <fonts count="17">
     <font>
@@ -455,12 +470,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -476,7 +488,11 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="164" fontId="16" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="167" fontId="15" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="19">
     <cellStyle name="Accent" xfId="2" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -513,9 +529,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -553,7 +569,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -659,7 +675,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -801,7 +817,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -812,19 +828,19 @@
   <dimension ref="A2:I52"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="9.83203125" customWidth="1"/>
-    <col min="2" max="2" width="6.33203125" customWidth="1"/>
+    <col min="1" max="1" width="9.796875" customWidth="1"/>
+    <col min="2" max="2" width="6.296875" customWidth="1"/>
     <col min="3" max="3" width="12.5" customWidth="1"/>
-    <col min="4" max="4" width="10.83203125" customWidth="1"/>
-    <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="11.1640625" customWidth="1"/>
-    <col min="7" max="7" width="10.1640625" customWidth="1"/>
-    <col min="8" max="8" width="11.83203125" customWidth="1"/>
-    <col min="9" max="9" width="9.1640625" customWidth="1"/>
-    <col min="10" max="1024" width="9.6640625" customWidth="1"/>
+    <col min="4" max="4" width="10.796875" customWidth="1"/>
+    <col min="5" max="5" width="12" style="9" customWidth="1"/>
+    <col min="6" max="6" width="11.19921875" style="9" customWidth="1"/>
+    <col min="7" max="7" width="10.19921875" style="9" customWidth="1"/>
+    <col min="8" max="8" width="11.796875" style="9" customWidth="1"/>
+    <col min="9" max="9" width="9.19921875" style="9" customWidth="1"/>
+    <col min="10" max="1024" width="9.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:9" s="3" customFormat="1" ht="24.75" customHeight="1">
+    <row r="2" spans="1:9" s="2" customFormat="1" ht="24.75" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -837,975 +853,1425 @@
       <c r="D2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="7" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="12.75" customHeight="1">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="7">
+      <c r="C3" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="6">
         <v>54721</v>
       </c>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
+      <c r="E3" s="8">
+        <f>IF(D3&lt;38000,4*22*9,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F3" s="8">
+        <f>IF(D3&lt;45000,5*22*9,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G3" s="8">
+        <f t="shared" ref="G3:G5" si="0">IF(OR(D3&lt;36000,C3="Sobresaliente"),35764*75%,IF(AND(D3&lt;45000,C3="Aprobado"),35764*25%,IF(AND(D3&lt;54000,C3="Notable"),35764*50%,0)))</f>
+        <v>0</v>
+      </c>
       <c r="H3" s="8"/>
       <c r="I3" s="8"/>
     </row>
     <row r="4" spans="1:9" ht="12.75" customHeight="1">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="7">
+      <c r="D4" s="6">
         <v>78656</v>
       </c>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
+      <c r="E4" s="8">
+        <f t="shared" ref="E4:E52" si="1">IF(D4&lt;38000,4*22*9,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F4" s="8">
+        <f t="shared" ref="F4:F52" si="2">IF(D4&lt;45000,5*22*9,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G4" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="H4" s="8"/>
       <c r="I4" s="8"/>
     </row>
     <row r="5" spans="1:9" ht="12.75" customHeight="1">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="7">
+      <c r="B5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="6">
         <v>94697</v>
       </c>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
+      <c r="E5" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F5" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G5" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="H5" s="8"/>
       <c r="I5" s="8"/>
     </row>
     <row r="6" spans="1:9" ht="12.75" customHeight="1">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" s="7">
+      <c r="B6" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="6">
         <v>35220</v>
       </c>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
+      <c r="E6" s="8">
+        <f t="shared" si="1"/>
+        <v>792</v>
+      </c>
+      <c r="F6" s="8">
+        <f t="shared" si="2"/>
+        <v>990</v>
+      </c>
+      <c r="G6" s="8">
+        <f>IF(OR(D6&lt;36000,C6="Sobresaliente"),35764*75%,IF(AND(D6&lt;45000,C6="Aprobado"),35764*25%,IF(AND(D6&lt;54000,C6="Notable"),35764*50%,0)))</f>
+        <v>26823</v>
+      </c>
       <c r="H6" s="8"/>
       <c r="I6" s="8"/>
     </row>
     <row r="7" spans="1:9" ht="12.75" customHeight="1">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D7" s="7">
+      <c r="B7" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" s="6">
         <v>62659</v>
       </c>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
+      <c r="E7" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F7" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G7" s="8">
+        <f t="shared" ref="G7:G52" si="3">IF(OR(D7&lt;36000,C7="Sobresaliente"),35764*75%,IF(AND(D7&lt;45000,C7="Aprobado"),35764*25%,IF(AND(D7&lt;54000,C7="Notable"),35764*50%,0)))</f>
+        <v>0</v>
+      </c>
       <c r="H7" s="8"/>
       <c r="I7" s="8"/>
     </row>
     <row r="8" spans="1:9" ht="12.75" customHeight="1">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" s="6" t="s">
+      <c r="B8" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="6">
         <v>37102</v>
       </c>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
+      <c r="E8" s="8">
+        <f t="shared" si="1"/>
+        <v>792</v>
+      </c>
+      <c r="F8" s="8">
+        <f t="shared" si="2"/>
+        <v>990</v>
+      </c>
+      <c r="G8" s="8">
+        <f t="shared" si="3"/>
+        <v>26823</v>
+      </c>
       <c r="H8" s="8"/>
       <c r="I8" s="8"/>
     </row>
     <row r="9" spans="1:9" ht="12.75" customHeight="1">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D9" s="7">
+      <c r="C9" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" s="6">
         <v>32186</v>
       </c>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
+      <c r="E9" s="8">
+        <f t="shared" si="1"/>
+        <v>792</v>
+      </c>
+      <c r="F9" s="8">
+        <f t="shared" si="2"/>
+        <v>990</v>
+      </c>
+      <c r="G9" s="8">
+        <f t="shared" si="3"/>
+        <v>26823</v>
+      </c>
       <c r="H9" s="8"/>
       <c r="I9" s="8"/>
     </row>
     <row r="10" spans="1:9" ht="12.75" customHeight="1">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="7">
+      <c r="D10" s="6">
         <v>102123</v>
       </c>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
+      <c r="E10" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F10" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G10" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="H10" s="8"/>
       <c r="I10" s="8"/>
     </row>
     <row r="11" spans="1:9" ht="12.75" customHeight="1">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D11" s="7">
+      <c r="D11" s="6">
         <v>105686</v>
       </c>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
+      <c r="E11" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F11" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G11" s="8">
+        <f t="shared" si="3"/>
+        <v>26823</v>
+      </c>
       <c r="H11" s="8"/>
       <c r="I11" s="8"/>
     </row>
     <row r="12" spans="1:9" ht="12.75" customHeight="1">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C12" s="6" t="s">
+      <c r="B12" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D12" s="7">
+      <c r="D12" s="6">
         <v>56704</v>
       </c>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
+      <c r="E12" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F12" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G12" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="H12" s="8"/>
       <c r="I12" s="8"/>
     </row>
     <row r="13" spans="1:9" ht="12.75" customHeight="1">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D13" s="7">
+      <c r="B13" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13" s="6">
         <v>100731</v>
       </c>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8"/>
+      <c r="E13" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F13" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G13" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="H13" s="8"/>
       <c r="I13" s="8"/>
     </row>
     <row r="14" spans="1:9" ht="12.75" customHeight="1">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D14" s="7">
+      <c r="D14" s="6">
         <v>38970</v>
       </c>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="8"/>
+      <c r="E14" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F14" s="8">
+        <f t="shared" si="2"/>
+        <v>990</v>
+      </c>
+      <c r="G14" s="8">
+        <f t="shared" si="3"/>
+        <v>8941</v>
+      </c>
       <c r="H14" s="8"/>
       <c r="I14" s="8"/>
     </row>
     <row r="15" spans="1:9" ht="12.75" customHeight="1">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C15" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D15" s="7">
+      <c r="C15" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D15" s="6">
         <v>88500</v>
       </c>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8"/>
+      <c r="E15" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F15" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G15" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="H15" s="8"/>
       <c r="I15" s="8"/>
     </row>
     <row r="16" spans="1:9" ht="12.75" customHeight="1">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D16" s="7">
+      <c r="D16" s="6">
         <v>71128</v>
       </c>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
-      <c r="G16" s="8"/>
+      <c r="E16" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F16" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G16" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="H16" s="8"/>
       <c r="I16" s="8"/>
     </row>
     <row r="17" spans="1:9" ht="12.75" customHeight="1">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C17" s="6" t="s">
+      <c r="B17" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D17" s="7">
+      <c r="D17" s="6">
         <v>70787</v>
       </c>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
-      <c r="G17" s="8"/>
+      <c r="E17" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F17" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G17" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="H17" s="8"/>
       <c r="I17" s="8"/>
     </row>
     <row r="18" spans="1:9" ht="12.75" customHeight="1">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C18" s="6" t="s">
+      <c r="B18" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C18" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D18" s="7">
+      <c r="D18" s="6">
         <v>41796</v>
       </c>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
-      <c r="G18" s="8"/>
+      <c r="E18" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F18" s="8">
+        <f t="shared" si="2"/>
+        <v>990</v>
+      </c>
+      <c r="G18" s="8">
+        <f t="shared" si="3"/>
+        <v>26823</v>
+      </c>
       <c r="H18" s="8"/>
       <c r="I18" s="8"/>
     </row>
     <row r="19" spans="1:9" ht="12.75" customHeight="1">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D19" s="7">
+      <c r="B19" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D19" s="6">
         <v>90489</v>
       </c>
-      <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
-      <c r="G19" s="8"/>
+      <c r="E19" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F19" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G19" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="H19" s="8"/>
       <c r="I19" s="8"/>
     </row>
     <row r="20" spans="1:9" ht="12.75" customHeight="1">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D20" s="7">
+      <c r="B20" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D20" s="6">
         <v>84143</v>
       </c>
-      <c r="E20" s="8"/>
-      <c r="F20" s="8"/>
-      <c r="G20" s="8"/>
+      <c r="E20" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F20" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G20" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="H20" s="8"/>
       <c r="I20" s="8"/>
     </row>
     <row r="21" spans="1:9" ht="12.75" customHeight="1">
-      <c r="A21" s="4" t="s">
+      <c r="A21" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C21" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D21" s="7">
+      <c r="C21" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D21" s="6">
         <v>71099</v>
       </c>
-      <c r="E21" s="8"/>
-      <c r="F21" s="8"/>
-      <c r="G21" s="8"/>
+      <c r="E21" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F21" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G21" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="H21" s="8"/>
       <c r="I21" s="8"/>
     </row>
     <row r="22" spans="1:9" ht="12.75" customHeight="1">
-      <c r="A22" s="4" t="s">
+      <c r="A22" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="C22" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D22" s="7">
+      <c r="D22" s="6">
         <v>75573</v>
       </c>
-      <c r="E22" s="8"/>
-      <c r="F22" s="8"/>
-      <c r="G22" s="8"/>
+      <c r="E22" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F22" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G22" s="8">
+        <f t="shared" si="3"/>
+        <v>26823</v>
+      </c>
       <c r="H22" s="8"/>
       <c r="I22" s="8"/>
     </row>
     <row r="23" spans="1:9" ht="12.75" customHeight="1">
-      <c r="A23" s="4" t="s">
+      <c r="A23" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C23" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D23" s="7">
+      <c r="C23" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D23" s="6">
         <v>51976</v>
       </c>
-      <c r="E23" s="8"/>
-      <c r="F23" s="8"/>
-      <c r="G23" s="8"/>
+      <c r="E23" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F23" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G23" s="8">
+        <f t="shared" si="3"/>
+        <v>17882</v>
+      </c>
       <c r="H23" s="8"/>
       <c r="I23" s="8"/>
     </row>
     <row r="24" spans="1:9" ht="12.75" customHeight="1">
-      <c r="A24" s="4" t="s">
+      <c r="A24" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D24" s="7">
+      <c r="B24" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D24" s="6">
         <v>84502</v>
       </c>
-      <c r="E24" s="8"/>
-      <c r="F24" s="8"/>
-      <c r="G24" s="8"/>
+      <c r="E24" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F24" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G24" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="H24" s="8"/>
       <c r="I24" s="8"/>
     </row>
     <row r="25" spans="1:9" ht="12.75" customHeight="1">
-      <c r="A25" s="4" t="s">
+      <c r="A25" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D25" s="7">
+      <c r="B25" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D25" s="6">
         <v>105822</v>
       </c>
-      <c r="E25" s="8"/>
-      <c r="F25" s="8"/>
-      <c r="G25" s="8"/>
+      <c r="E25" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F25" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G25" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="H25" s="8"/>
       <c r="I25" s="8"/>
     </row>
     <row r="26" spans="1:9" ht="12.75" customHeight="1">
-      <c r="A26" s="4" t="s">
+      <c r="A26" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C26" s="6" t="s">
+      <c r="B26" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C26" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D26" s="7">
+      <c r="D26" s="6">
         <v>36940</v>
       </c>
-      <c r="E26" s="8"/>
-      <c r="F26" s="8"/>
-      <c r="G26" s="8"/>
+      <c r="E26" s="8">
+        <f t="shared" si="1"/>
+        <v>792</v>
+      </c>
+      <c r="F26" s="8">
+        <f t="shared" si="2"/>
+        <v>990</v>
+      </c>
+      <c r="G26" s="8">
+        <f t="shared" si="3"/>
+        <v>8941</v>
+      </c>
       <c r="H26" s="8"/>
       <c r="I26" s="8"/>
     </row>
     <row r="27" spans="1:9" ht="12.75" customHeight="1">
-      <c r="A27" s="4" t="s">
+      <c r="A27" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D27" s="7">
+      <c r="B27" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D27" s="6">
         <v>94168</v>
       </c>
-      <c r="E27" s="8"/>
-      <c r="F27" s="8"/>
-      <c r="G27" s="8"/>
+      <c r="E27" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F27" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G27" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="H27" s="8"/>
       <c r="I27" s="8"/>
     </row>
     <row r="28" spans="1:9" ht="12.75" customHeight="1">
-      <c r="A28" s="4" t="s">
+      <c r="A28" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D28" s="7">
+      <c r="B28" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D28" s="6">
         <v>89430</v>
       </c>
-      <c r="E28" s="8"/>
-      <c r="F28" s="8"/>
-      <c r="G28" s="8"/>
+      <c r="E28" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F28" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G28" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="H28" s="8"/>
       <c r="I28" s="8"/>
     </row>
     <row r="29" spans="1:9" ht="12.75" customHeight="1">
-      <c r="A29" s="4" t="s">
+      <c r="A29" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B29" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C29" s="6" t="s">
+      <c r="C29" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D29" s="7">
+      <c r="D29" s="6">
         <v>78611</v>
       </c>
-      <c r="E29" s="8"/>
-      <c r="F29" s="8"/>
-      <c r="G29" s="8"/>
+      <c r="E29" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F29" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G29" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="H29" s="8"/>
       <c r="I29" s="8"/>
     </row>
     <row r="30" spans="1:9" ht="12.75" customHeight="1">
-      <c r="A30" s="4" t="s">
+      <c r="A30" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B30" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C30" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D30" s="7">
+      <c r="B30" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D30" s="6">
         <v>87686</v>
       </c>
-      <c r="E30" s="8"/>
-      <c r="F30" s="8"/>
-      <c r="G30" s="8"/>
+      <c r="E30" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F30" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G30" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="H30" s="8"/>
       <c r="I30" s="8"/>
     </row>
     <row r="31" spans="1:9" ht="12.75" customHeight="1">
-      <c r="A31" s="4" t="s">
+      <c r="A31" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B31" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C31" s="6" t="s">
+      <c r="B31" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C31" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D31" s="7">
+      <c r="D31" s="6">
         <v>106285</v>
       </c>
-      <c r="E31" s="8"/>
-      <c r="F31" s="8"/>
-      <c r="G31" s="8"/>
+      <c r="E31" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F31" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G31" s="8">
+        <f t="shared" si="3"/>
+        <v>26823</v>
+      </c>
       <c r="H31" s="8"/>
       <c r="I31" s="8"/>
     </row>
     <row r="32" spans="1:9" ht="12.75" customHeight="1">
-      <c r="A32" s="4" t="s">
+      <c r="A32" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B32" s="5" t="s">
+      <c r="B32" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C32" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D32" s="7">
+      <c r="C32" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D32" s="6">
         <v>50954</v>
       </c>
-      <c r="E32" s="8"/>
-      <c r="F32" s="8"/>
-      <c r="G32" s="8"/>
+      <c r="E32" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F32" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G32" s="8">
+        <f t="shared" si="3"/>
+        <v>17882</v>
+      </c>
       <c r="H32" s="8"/>
       <c r="I32" s="8"/>
     </row>
     <row r="33" spans="1:9" ht="12.75" customHeight="1">
-      <c r="A33" s="4" t="s">
+      <c r="A33" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="B33" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C33" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D33" s="7">
+      <c r="C33" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D33" s="6">
         <v>38170</v>
       </c>
-      <c r="E33" s="8"/>
-      <c r="F33" s="8"/>
-      <c r="G33" s="8"/>
+      <c r="E33" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F33" s="8">
+        <f t="shared" si="2"/>
+        <v>990</v>
+      </c>
+      <c r="G33" s="8">
+        <f t="shared" si="3"/>
+        <v>17882</v>
+      </c>
       <c r="H33" s="8"/>
       <c r="I33" s="8"/>
     </row>
     <row r="34" spans="1:9" ht="12.75" customHeight="1">
-      <c r="A34" s="4" t="s">
+      <c r="A34" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B34" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C34" s="6" t="s">
+      <c r="B34" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C34" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D34" s="7">
+      <c r="D34" s="6">
         <v>63047</v>
       </c>
-      <c r="E34" s="8"/>
-      <c r="F34" s="8"/>
-      <c r="G34" s="8"/>
+      <c r="E34" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F34" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G34" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="H34" s="8"/>
       <c r="I34" s="8"/>
     </row>
     <row r="35" spans="1:9" ht="12.75" customHeight="1">
-      <c r="A35" s="4" t="s">
+      <c r="A35" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B35" s="5" t="s">
+      <c r="B35" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C35" s="6" t="s">
+      <c r="C35" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D35" s="7">
+      <c r="D35" s="6">
         <v>84400</v>
       </c>
-      <c r="E35" s="8"/>
-      <c r="F35" s="8"/>
-      <c r="G35" s="8"/>
+      <c r="E35" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F35" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G35" s="8">
+        <f t="shared" si="3"/>
+        <v>26823</v>
+      </c>
       <c r="H35" s="8"/>
       <c r="I35" s="8"/>
     </row>
     <row r="36" spans="1:9" ht="12.75" customHeight="1">
-      <c r="A36" s="4" t="s">
+      <c r="A36" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="B36" s="5" t="s">
+      <c r="B36" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C36" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D36" s="7">
+      <c r="C36" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D36" s="6">
         <v>30750</v>
       </c>
-      <c r="E36" s="8"/>
-      <c r="F36" s="8"/>
-      <c r="G36" s="8"/>
+      <c r="E36" s="8">
+        <f t="shared" si="1"/>
+        <v>792</v>
+      </c>
+      <c r="F36" s="8">
+        <f t="shared" si="2"/>
+        <v>990</v>
+      </c>
+      <c r="G36" s="8">
+        <f t="shared" si="3"/>
+        <v>26823</v>
+      </c>
       <c r="H36" s="8"/>
       <c r="I36" s="8"/>
     </row>
     <row r="37" spans="1:9" ht="12.75" customHeight="1">
-      <c r="A37" s="4" t="s">
+      <c r="A37" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B37" s="5" t="s">
+      <c r="B37" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C37" s="6" t="s">
+      <c r="C37" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D37" s="7">
+      <c r="D37" s="6">
         <v>32946</v>
       </c>
-      <c r="E37" s="8"/>
-      <c r="F37" s="8"/>
-      <c r="G37" s="8"/>
+      <c r="E37" s="8">
+        <f t="shared" si="1"/>
+        <v>792</v>
+      </c>
+      <c r="F37" s="8">
+        <f t="shared" si="2"/>
+        <v>990</v>
+      </c>
+      <c r="G37" s="8">
+        <f t="shared" si="3"/>
+        <v>26823</v>
+      </c>
       <c r="H37" s="8"/>
       <c r="I37" s="8"/>
     </row>
     <row r="38" spans="1:9" ht="12.75" customHeight="1">
-      <c r="A38" s="4" t="s">
+      <c r="A38" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B38" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C38" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D38" s="7">
+      <c r="B38" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D38" s="6">
         <v>88517</v>
       </c>
-      <c r="E38" s="8"/>
-      <c r="F38" s="8"/>
-      <c r="G38" s="8"/>
+      <c r="E38" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F38" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G38" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="H38" s="8"/>
       <c r="I38" s="8"/>
     </row>
     <row r="39" spans="1:9" ht="12.75" customHeight="1">
-      <c r="A39" s="4" t="s">
+      <c r="A39" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B39" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C39" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D39" s="7">
+      <c r="B39" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D39" s="6">
         <v>77409</v>
       </c>
-      <c r="E39" s="8"/>
-      <c r="F39" s="8"/>
-      <c r="G39" s="8"/>
+      <c r="E39" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F39" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G39" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="H39" s="8"/>
       <c r="I39" s="8"/>
     </row>
     <row r="40" spans="1:9" ht="12.75" customHeight="1">
-      <c r="A40" s="4" t="s">
+      <c r="A40" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B40" s="5" t="s">
+      <c r="B40" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C40" s="6" t="s">
+      <c r="C40" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D40" s="7">
+      <c r="D40" s="6">
         <v>64913</v>
       </c>
-      <c r="E40" s="8"/>
-      <c r="F40" s="8"/>
-      <c r="G40" s="8"/>
+      <c r="E40" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F40" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G40" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="H40" s="8"/>
       <c r="I40" s="8"/>
     </row>
     <row r="41" spans="1:9" ht="12.75" customHeight="1">
-      <c r="A41" s="4" t="s">
+      <c r="A41" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B41" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C41" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D41" s="7">
+      <c r="B41" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D41" s="6">
         <v>51429</v>
       </c>
-      <c r="E41" s="8"/>
-      <c r="F41" s="8"/>
-      <c r="G41" s="8"/>
+      <c r="E41" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F41" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G41" s="8">
+        <f t="shared" si="3"/>
+        <v>17882</v>
+      </c>
       <c r="H41" s="8"/>
       <c r="I41" s="8"/>
     </row>
     <row r="42" spans="1:9" ht="12.75" customHeight="1">
-      <c r="A42" s="4" t="s">
+      <c r="A42" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B42" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C42" s="6" t="s">
+      <c r="B42" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C42" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D42" s="7">
+      <c r="D42" s="6">
         <v>96437</v>
       </c>
-      <c r="E42" s="8"/>
-      <c r="F42" s="8"/>
-      <c r="G42" s="8"/>
+      <c r="E42" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F42" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G42" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="H42" s="8"/>
       <c r="I42" s="8"/>
     </row>
     <row r="43" spans="1:9" ht="12.75" customHeight="1">
-      <c r="A43" s="4" t="s">
+      <c r="A43" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B43" s="5" t="s">
+      <c r="B43" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C43" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D43" s="7">
+      <c r="C43" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D43" s="6">
         <v>77318</v>
       </c>
-      <c r="E43" s="8"/>
-      <c r="F43" s="8"/>
-      <c r="G43" s="8"/>
+      <c r="E43" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F43" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G43" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="H43" s="8"/>
       <c r="I43" s="8"/>
     </row>
     <row r="44" spans="1:9" ht="12.75" customHeight="1">
-      <c r="A44" s="4" t="s">
+      <c r="A44" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="B44" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C44" s="6" t="s">
+      <c r="B44" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C44" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D44" s="7">
+      <c r="D44" s="6">
         <v>81740</v>
       </c>
-      <c r="E44" s="8"/>
-      <c r="F44" s="8"/>
-      <c r="G44" s="8"/>
+      <c r="E44" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F44" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G44" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="H44" s="8"/>
       <c r="I44" s="8"/>
     </row>
     <row r="45" spans="1:9" ht="12.75" customHeight="1">
-      <c r="A45" s="4" t="s">
+      <c r="A45" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B45" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C45" s="6" t="s">
+      <c r="B45" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C45" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D45" s="7">
+      <c r="D45" s="6">
         <v>33985</v>
       </c>
-      <c r="E45" s="8"/>
-      <c r="F45" s="8"/>
-      <c r="G45" s="8"/>
+      <c r="E45" s="8">
+        <f t="shared" si="1"/>
+        <v>792</v>
+      </c>
+      <c r="F45" s="8">
+        <f t="shared" si="2"/>
+        <v>990</v>
+      </c>
+      <c r="G45" s="8">
+        <f t="shared" si="3"/>
+        <v>26823</v>
+      </c>
       <c r="H45" s="8"/>
       <c r="I45" s="8"/>
     </row>
     <row r="46" spans="1:9" ht="12.75" customHeight="1">
-      <c r="A46" s="4" t="s">
+      <c r="A46" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B46" s="5" t="s">
+      <c r="B46" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C46" s="6" t="s">
+      <c r="C46" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D46" s="7">
+      <c r="D46" s="6">
         <v>97816</v>
       </c>
-      <c r="E46" s="8"/>
-      <c r="F46" s="8"/>
-      <c r="G46" s="8"/>
+      <c r="E46" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F46" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G46" s="8">
+        <f t="shared" si="3"/>
+        <v>26823</v>
+      </c>
       <c r="H46" s="8"/>
       <c r="I46" s="8"/>
     </row>
     <row r="47" spans="1:9" ht="12.75" customHeight="1">
-      <c r="A47" s="4" t="s">
+      <c r="A47" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B47" s="5" t="s">
+      <c r="B47" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C47" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D47" s="7">
+      <c r="C47" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D47" s="6">
         <v>37262</v>
       </c>
-      <c r="E47" s="8"/>
-      <c r="F47" s="8"/>
-      <c r="G47" s="8"/>
+      <c r="E47" s="8">
+        <f t="shared" si="1"/>
+        <v>792</v>
+      </c>
+      <c r="F47" s="8">
+        <f t="shared" si="2"/>
+        <v>990</v>
+      </c>
+      <c r="G47" s="8">
+        <f t="shared" si="3"/>
+        <v>17882</v>
+      </c>
       <c r="H47" s="8"/>
       <c r="I47" s="8"/>
     </row>
     <row r="48" spans="1:9" ht="12.75" customHeight="1">
-      <c r="A48" s="4" t="s">
+      <c r="A48" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B48" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C48" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D48" s="7">
+      <c r="B48" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D48" s="6">
         <v>30941</v>
       </c>
-      <c r="E48" s="8"/>
-      <c r="F48" s="8"/>
-      <c r="G48" s="8"/>
+      <c r="E48" s="8">
+        <f t="shared" si="1"/>
+        <v>792</v>
+      </c>
+      <c r="F48" s="8">
+        <f t="shared" si="2"/>
+        <v>990</v>
+      </c>
+      <c r="G48" s="8">
+        <f t="shared" si="3"/>
+        <v>26823</v>
+      </c>
       <c r="H48" s="8"/>
       <c r="I48" s="8"/>
     </row>
     <row r="49" spans="1:9" ht="12.75" customHeight="1">
-      <c r="A49" s="4" t="s">
+      <c r="A49" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B49" s="5" t="s">
+      <c r="B49" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C49" s="6" t="s">
+      <c r="C49" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D49" s="7">
+      <c r="D49" s="6">
         <v>56271</v>
       </c>
-      <c r="E49" s="8"/>
-      <c r="F49" s="8"/>
-      <c r="G49" s="8"/>
+      <c r="E49" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F49" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G49" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="H49" s="8"/>
       <c r="I49" s="8"/>
     </row>
     <row r="50" spans="1:9" ht="12.75" customHeight="1">
-      <c r="A50" s="4" t="s">
+      <c r="A50" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B50" s="5" t="s">
+      <c r="B50" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C50" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D50" s="7">
+      <c r="C50" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D50" s="6">
         <v>52511</v>
       </c>
-      <c r="E50" s="8"/>
-      <c r="F50" s="8"/>
-      <c r="G50" s="8"/>
+      <c r="E50" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F50" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G50" s="8">
+        <f t="shared" si="3"/>
+        <v>17882</v>
+      </c>
       <c r="H50" s="8"/>
       <c r="I50" s="8"/>
     </row>
     <row r="51" spans="1:9" ht="12.75" customHeight="1">
-      <c r="A51" s="4" t="s">
+      <c r="A51" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B51" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C51" s="6" t="s">
+      <c r="B51" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C51" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D51" s="7">
+      <c r="D51" s="6">
         <v>58814</v>
       </c>
-      <c r="E51" s="8"/>
-      <c r="F51" s="8"/>
-      <c r="G51" s="8"/>
+      <c r="E51" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F51" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G51" s="8">
+        <f t="shared" si="3"/>
+        <v>26823</v>
+      </c>
       <c r="H51" s="8"/>
       <c r="I51" s="8"/>
     </row>
     <row r="52" spans="1:9" ht="12.75" customHeight="1">
-      <c r="A52" s="4" t="s">
+      <c r="A52" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B52" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C52" s="6" t="s">
+      <c r="B52" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C52" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D52" s="7">
+      <c r="D52" s="6">
         <v>98439</v>
       </c>
-      <c r="E52" s="8"/>
-      <c r="F52" s="8"/>
-      <c r="G52" s="8"/>
+      <c r="E52" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F52" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G52" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="H52" s="8"/>
       <c r="I52" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="1.2791338582677163" bottom="1.2791338582677163" header="0.98385826771653528" footer="0.98385826771653528"/>
-  <pageSetup paperSize="0" fitToWidth="0" fitToHeight="0" pageOrder="overThenDown" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="0"/>
+  <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" pageOrder="overThenDown" orientation="portrait" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>